--- a/excel/Forwards_Market_Making_Simulator.xlsx
+++ b/excel/Forwards_Market_Making_Simulator.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="277">
   <si>
     <t xml:space="preserve">Forwards Market-Making Simulator</t>
   </si>
@@ -67,7 +67,7 @@
     <t xml:space="preserve">1. Choose an instrument</t>
   </si>
   <si>
-    <t xml:space="preserve">Inputs!C4 is a dropdown of 7 FX pairs, 5 commodities and one Custom row. Everything (pricing, quote size, spread, limits, labels, charts) re-prices when you change it.</t>
+    <t xml:space="preserve">Inputs!C4 is a dropdown of 7 FX pairs, 6 commodities and one Custom row. Everything (pricing, quote size, spread, limits, labels, charts) re-prices when you change it.</t>
   </si>
   <si>
     <t xml:space="preserve">2. Tweak assumptions</t>
@@ -578,6 +578,12 @@
   </si>
   <si>
     <t xml:space="preserve">Price USD/bbl, 90-day forward. Conv. yield 7.00% &gt; carry 6.00% -&gt; mild BACKWARDATION (forward &lt; spot). Illustrative.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brent Crude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price USD/bbl (ICE Brent), 90-day forward. Conv. yield 7.00% &gt; carry 6.00% -&gt; mild BACKWARDATION. Illustrative.</t>
   </si>
   <si>
     <t xml:space="preserve">Copper</t>
@@ -2091,11 +2097,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="39611499"/>
-        <c:axId val="99411063"/>
+        <c:axId val="24287577"/>
+        <c:axId val="28259607"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="39611499"/>
+        <c:axId val="24287577"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2161,7 +2167,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99411063"/>
+        <c:crossAx val="28259607"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2169,7 +2175,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="99411063"/>
+        <c:axId val="28259607"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2245,7 +2251,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39611499"/>
+        <c:crossAx val="24287577"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2763,11 +2769,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="32424155"/>
-        <c:axId val="62798474"/>
+        <c:axId val="90674721"/>
+        <c:axId val="37613774"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="32424155"/>
+        <c:axId val="90674721"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2833,7 +2839,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62798474"/>
+        <c:crossAx val="37613774"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2841,7 +2847,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="62798474"/>
+        <c:axId val="37613774"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2917,7 +2923,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32424155"/>
+        <c:crossAx val="90674721"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3487,7 +3493,7 @@
         <v>60</v>
       </c>
       <c r="C5" s="9" t="n">
-        <f aca="false">MATCH(Instrument,Instruments!$B$6:$B$18,0)</f>
+        <f aca="false">MATCH(Instrument,Instruments!$B$6:$B$19,0)</f>
         <v>1</v>
       </c>
     </row>
@@ -3496,7 +3502,7 @@
         <v>61</v>
       </c>
       <c r="C6" s="2" t="str">
-        <f aca="false">INDEX(Instruments!$Y$6:$Y$18,Inst_Row)</f>
+        <f aca="false">INDEX(Instruments!$Y$6:$Y$19,Inst_Row)</f>
         <v>Original project brief: USD 4.00%, SGD 0.55%, 45-day tenor, USD 250k, 5-tick spread. Spot illustrative.</v>
       </c>
     </row>
@@ -3505,7 +3511,7 @@
         <v>62</v>
       </c>
       <c r="C7" s="6" t="str">
-        <f aca="false">IF(AND(Use_Live_Spot=1,ISNUMBER(INDEX(Live!$C$6:$C$18,Inst_Row))),"LIVE spot, as of "&amp;INDEX(Live!$D$6:$D$18,Inst_Row)&amp;"  ["&amp;INDEX(Live!$E$6:$E$18,Inst_Row)&amp;"]","Library spot (illustrative placeholder)")</f>
+        <f aca="false">IF(AND(Use_Live_Spot=1,ISNUMBER(INDEX(Live!$C$6:$C$19,Inst_Row))),"LIVE spot, as of "&amp;INDEX(Live!$D$6:$D$19,Inst_Row)&amp;"  ["&amp;INDEX(Live!$E$6:$E$19,Inst_Row)&amp;"]","Library spot (illustrative placeholder)")</f>
         <v>Library spot (illustrative placeholder)</v>
       </c>
     </row>
@@ -3544,7 +3550,7 @@
         <v>70</v>
       </c>
       <c r="C10" s="12" t="str">
-        <f aca="false">INDEX(Instruments!$C$6:$C$18,Inst_Row)</f>
+        <f aca="false">INDEX(Instruments!$C$6:$C$19,Inst_Row)</f>
         <v>FX</v>
       </c>
       <c r="D10" s="13" t="s">
@@ -3563,7 +3569,7 @@
         <v>73</v>
       </c>
       <c r="C11" s="12" t="str">
-        <f aca="false">INDEX(Instruments!$D$6:$D$18,Inst_Row)</f>
+        <f aca="false">INDEX(Instruments!$D$6:$D$19,Inst_Row)</f>
         <v>USD</v>
       </c>
       <c r="D11" s="13" t="s">
@@ -3582,7 +3588,7 @@
         <v>75</v>
       </c>
       <c r="C12" s="12" t="str">
-        <f aca="false">INDEX(Instruments!$E$6:$E$18,Inst_Row)</f>
+        <f aca="false">INDEX(Instruments!$E$6:$E$19,Inst_Row)</f>
         <v>SGD</v>
       </c>
       <c r="D12" s="13" t="s">
@@ -3611,7 +3617,7 @@
         <v>77</v>
       </c>
       <c r="C14" s="15" t="n">
-        <f aca="false">IF(AND(Use_Live_Spot=1,ISNUMBER(INDEX(Live!$C$6:$C$18,Inst_Row))),INDEX(Live!$C$6:$C$18,Inst_Row),INDEX(Instruments!$F$6:$F$18,Inst_Row))</f>
+        <f aca="false">IF(AND(Use_Live_Spot=1,ISNUMBER(INDEX(Live!$C$6:$C$19,Inst_Row))),INDEX(Live!$C$6:$C$19,Inst_Row),INDEX(Instruments!$F$6:$F$19,Inst_Row))</f>
         <v>1.285</v>
       </c>
       <c r="D14" s="16"/>
@@ -3653,7 +3659,7 @@
         <v>Rate A: base-currency interest rate</v>
       </c>
       <c r="C16" s="19" t="n">
-        <f aca="false">INDEX(Instruments!$G$6:$G$18,Inst_Row)</f>
+        <f aca="false">INDEX(Instruments!$G$6:$G$19,Inst_Row)</f>
         <v>0.04</v>
       </c>
       <c r="D16" s="20"/>
@@ -3674,7 +3680,7 @@
         <v>Rate B: quote-currency interest rate</v>
       </c>
       <c r="C17" s="19" t="n">
-        <f aca="false">INDEX(Instruments!$J$6:$J$18,Inst_Row)</f>
+        <f aca="false">INDEX(Instruments!$J$6:$J$19,Inst_Row)</f>
         <v>0.0055</v>
       </c>
       <c r="D17" s="20"/>
@@ -3694,7 +3700,7 @@
         <v>85</v>
       </c>
       <c r="C18" s="22" t="n">
-        <f aca="false">INDEX(Instruments!$K$6:$K$18,Inst_Row)</f>
+        <f aca="false">INDEX(Instruments!$K$6:$K$19,Inst_Row)</f>
         <v>360</v>
       </c>
       <c r="D18" s="18"/>
@@ -3714,7 +3720,7 @@
         <v>88</v>
       </c>
       <c r="C19" s="22" t="n">
-        <f aca="false">INDEX(Instruments!$L$6:$L$18,Inst_Row)</f>
+        <f aca="false">INDEX(Instruments!$L$6:$L$19,Inst_Row)</f>
         <v>365</v>
       </c>
       <c r="D19" s="18"/>
@@ -3732,7 +3738,7 @@
         <v>89</v>
       </c>
       <c r="C20" s="22" t="n">
-        <f aca="false">INDEX(Instruments!$M$6:$M$18,Inst_Row)</f>
+        <f aca="false">INDEX(Instruments!$M$6:$M$19,Inst_Row)</f>
         <v>45</v>
       </c>
       <c r="D20" s="18"/>
@@ -3762,7 +3768,7 @@
         <v>92</v>
       </c>
       <c r="C22" s="24" t="n">
-        <f aca="false">INDEX(Instruments!$N$6:$N$18,Inst_Row)</f>
+        <f aca="false">INDEX(Instruments!$N$6:$N$19,Inst_Row)</f>
         <v>0.0001</v>
       </c>
       <c r="D22" s="25"/>
@@ -3783,7 +3789,7 @@
         <v>94</v>
       </c>
       <c r="C23" s="27" t="n">
-        <f aca="false">INDEX(Instruments!$O$6:$O$18,Inst_Row)</f>
+        <f aca="false">INDEX(Instruments!$O$6:$O$19,Inst_Row)</f>
         <v>250000</v>
       </c>
       <c r="D23" s="28"/>
@@ -3804,7 +3810,7 @@
         <v>96</v>
       </c>
       <c r="C24" s="30" t="n">
-        <f aca="false">INDEX(Instruments!$P$6:$P$18,Inst_Row)</f>
+        <f aca="false">INDEX(Instruments!$P$6:$P$19,Inst_Row)</f>
         <v>5</v>
       </c>
       <c r="D24" s="31"/>
@@ -3824,7 +3830,7 @@
         <v>99</v>
       </c>
       <c r="C25" s="30" t="n">
-        <f aca="false">INDEX(Instruments!$Q$6:$Q$18,Inst_Row)</f>
+        <f aca="false">INDEX(Instruments!$Q$6:$Q$19,Inst_Row)</f>
         <v>3</v>
       </c>
       <c r="D25" s="31"/>
@@ -3854,7 +3860,7 @@
         <v>102</v>
       </c>
       <c r="C27" s="27" t="n">
-        <f aca="false">INDEX(Instruments!$R$6:$R$18,Inst_Row)</f>
+        <f aca="false">INDEX(Instruments!$R$6:$R$19,Inst_Row)</f>
         <v>1000000</v>
       </c>
       <c r="D27" s="28"/>
@@ -3875,7 +3881,7 @@
         <v>104</v>
       </c>
       <c r="C28" s="27" t="n">
-        <f aca="false">INDEX(Instruments!$S$6:$S$18,Inst_Row)</f>
+        <f aca="false">INDEX(Instruments!$S$6:$S$19,Inst_Row)</f>
         <v>1800</v>
       </c>
       <c r="D28" s="28"/>
@@ -3896,7 +3902,7 @@
         <v>106</v>
       </c>
       <c r="C29" s="30" t="n">
-        <f aca="false">INDEX(Instruments!$T$6:$T$18,Inst_Row)</f>
+        <f aca="false">INDEX(Instruments!$T$6:$T$19,Inst_Row)</f>
         <v>1</v>
       </c>
       <c r="D29" s="31"/>
@@ -3985,7 +3991,7 @@
         <v>115</v>
       </c>
       <c r="C34" s="30" t="n">
-        <f aca="false">INDEX(Instruments!$U$6:$U$18,Inst_Row)</f>
+        <f aca="false">INDEX(Instruments!$U$6:$U$19,Inst_Row)</f>
         <v>3</v>
       </c>
       <c r="D34" s="31"/>
@@ -4024,7 +4030,7 @@
   </sheetData>
   <dataValidations count="3">
     <dataValidation allowBlank="false" error="Pick an instrument from the list." errorStyle="stop" errorTitle="Instrument" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C4" type="list">
-      <formula1>Instruments!$B$6:$B$18</formula1>
+      <formula1>Instruments!$B$6:$B$19</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E15" type="list">
@@ -4051,7 +4057,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:Y20"/>
+  <dimension ref="B1:Y21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -4945,26 +4951,26 @@
         <v>34</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E16" s="37" t="s">
         <v>145</v>
       </c>
       <c r="F16" s="38" t="n">
-        <v>10000</v>
+        <v>69</v>
       </c>
       <c r="G16" s="39" t="n">
-        <v>0.02</v>
+        <v>0.07</v>
       </c>
       <c r="H16" s="39" t="n">
         <v>0.04</v>
       </c>
       <c r="I16" s="39" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="J16" s="48" t="n">
         <f aca="false">H16+I16</f>
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="K16" s="41" t="n">
         <v>365</v>
@@ -4976,73 +4982,73 @@
         <v>90</v>
       </c>
       <c r="N16" s="42" t="n">
-        <v>0.5</v>
+        <v>0.01</v>
       </c>
       <c r="O16" s="43" t="n">
-        <v>25</v>
+        <v>10000</v>
       </c>
       <c r="P16" s="44" t="n">
         <v>4</v>
       </c>
       <c r="Q16" s="44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R16" s="43" t="n">
-        <v>100</v>
+        <v>40000</v>
       </c>
       <c r="S16" s="43" t="n">
-        <v>3000</v>
+        <v>19200</v>
       </c>
       <c r="T16" s="44" t="n">
         <v>1</v>
       </c>
       <c r="U16" s="44" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V16" s="45" t="n">
         <f aca="false">F16*(1+J16*M16/L16)/(1+G16*M16/K16)</f>
-        <v>10073.6095965104</v>
+        <v>68.832749798007</v>
       </c>
       <c r="W16" s="46" t="n">
         <f aca="false">(V16-F16)/N16</f>
-        <v>147.219193020719</v>
+        <v>-16.7250201992985</v>
       </c>
       <c r="X16" s="47" t="n">
         <f aca="false">(V16/F16-1)*365/M16</f>
-        <v>0.0298527808069793</v>
+        <v>-0.00983032588203544</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="36" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C17" s="37" t="s">
         <v>34</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E17" s="37" t="s">
         <v>145</v>
       </c>
       <c r="F17" s="38" t="n">
-        <v>3.5</v>
+        <v>10000</v>
       </c>
       <c r="G17" s="39" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="H17" s="39" t="n">
         <v>0.04</v>
       </c>
       <c r="I17" s="39" t="n">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
       <c r="J17" s="48" t="n">
         <f aca="false">H17+I17</f>
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="K17" s="41" t="n">
         <v>365</v>
@@ -5054,22 +5060,22 @@
         <v>90</v>
       </c>
       <c r="N17" s="42" t="n">
-        <v>0.001</v>
+        <v>0.5</v>
       </c>
       <c r="O17" s="43" t="n">
-        <v>10000</v>
+        <v>25</v>
       </c>
       <c r="P17" s="44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q17" s="44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R17" s="43" t="n">
-        <v>40000</v>
+        <v>100</v>
       </c>
       <c r="S17" s="43" t="n">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="T17" s="44" t="n">
         <v>1</v>
@@ -5079,104 +5085,182 @@
       </c>
       <c r="V17" s="45" t="n">
         <f aca="false">F17*(1+J17*M17/L17)/(1+G17*M17/K17)</f>
-        <v>3.63808219178082</v>
+        <v>10073.6095965104</v>
       </c>
       <c r="W17" s="46" t="n">
         <f aca="false">(V17-F17)/N17</f>
-        <v>138.082191780822</v>
+        <v>147.219193020719</v>
       </c>
       <c r="X17" s="47" t="n">
         <f aca="false">(V17/F17-1)*365/M17</f>
+        <v>0.0298527808069793</v>
+      </c>
+      <c r="Y17" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="36" t="s">
+        <v>180</v>
+      </c>
+      <c r="C18" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="E18" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="F18" s="38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G18" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="39" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I18" s="39" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J18" s="48" t="n">
+        <f aca="false">H18+I18</f>
         <v>0.16</v>
       </c>
-      <c r="Y17" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="49" t="s">
-        <v>181</v>
-      </c>
-      <c r="C18" s="50" t="s">
-        <v>144</v>
-      </c>
-      <c r="D18" s="50" t="s">
-        <v>145</v>
-      </c>
-      <c r="E18" s="50" t="s">
-        <v>182</v>
-      </c>
-      <c r="F18" s="51" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G18" s="52" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H18" s="40" t="s">
-        <v>147</v>
-      </c>
-      <c r="I18" s="40" t="s">
-        <v>147</v>
-      </c>
-      <c r="J18" s="52" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K18" s="53" t="n">
-        <v>360</v>
-      </c>
-      <c r="L18" s="53" t="n">
+      <c r="K18" s="41" t="n">
         <v>365</v>
       </c>
-      <c r="M18" s="53" t="n">
-        <v>45</v>
-      </c>
-      <c r="N18" s="54" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="O18" s="55" t="n">
-        <v>250000</v>
-      </c>
-      <c r="P18" s="56" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q18" s="56" t="n">
-        <v>4</v>
-      </c>
-      <c r="R18" s="55" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="S18" s="55" t="n">
-        <v>3000</v>
-      </c>
-      <c r="T18" s="56" t="n">
+      <c r="L18" s="41" t="n">
+        <v>365</v>
+      </c>
+      <c r="M18" s="41" t="n">
+        <v>90</v>
+      </c>
+      <c r="N18" s="42" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O18" s="43" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P18" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" s="43" t="n">
+        <v>40000</v>
+      </c>
+      <c r="S18" s="43" t="n">
+        <v>2400</v>
+      </c>
+      <c r="T18" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="U18" s="56" t="n">
-        <v>5</v>
+      <c r="U18" s="44" t="n">
+        <v>10</v>
       </c>
       <c r="V18" s="45" t="n">
         <f aca="false">F18*(1+J18*M18/L18)/(1+G18*M18/K18)</f>
-        <v>4.19456143937845</v>
+        <v>3.63808219178082</v>
       </c>
       <c r="W18" s="46" t="n">
         <f aca="false">(V18-F18)/N18</f>
-        <v>-54.3856062154902</v>
+        <v>138.082191780822</v>
       </c>
       <c r="X18" s="47" t="n">
         <f aca="false">(V18/F18-1)*365/M18</f>
+        <v>0.16</v>
+      </c>
+      <c r="Y18" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="49" t="s">
+        <v>183</v>
+      </c>
+      <c r="C19" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="D19" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="E19" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="F19" s="51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G19" s="52" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H19" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="I19" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="J19" s="52" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K19" s="53" t="n">
+        <v>360</v>
+      </c>
+      <c r="L19" s="53" t="n">
+        <v>365</v>
+      </c>
+      <c r="M19" s="53" t="n">
+        <v>45</v>
+      </c>
+      <c r="N19" s="54" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="O19" s="55" t="n">
+        <v>250000</v>
+      </c>
+      <c r="P19" s="56" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="R19" s="55" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="S19" s="55" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T19" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="V19" s="45" t="n">
+        <f aca="false">F19*(1+J19*M19/L19)/(1+G19*M19/K19)</f>
+        <v>4.19456143937845</v>
+      </c>
+      <c r="W19" s="46" t="n">
+        <f aca="false">(V19-F19)/N19</f>
+        <v>-54.3856062154902</v>
+      </c>
+      <c r="X19" s="47" t="n">
+        <f aca="false">(V19/F19-1)*365/M19</f>
         <v>-0.0105030403537849</v>
       </c>
-      <c r="Y18" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="2" t="s">
-        <v>184</v>
+      <c r="Y19" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="2" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B6:X18">
+  <conditionalFormatting sqref="B6:X19">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$B6=Instrument</formula>
     </cfRule>
@@ -5196,7 +5280,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:J18"/>
+  <dimension ref="B1:J19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -5212,17 +5296,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5230,28 +5314,28 @@
         <v>122</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H5" s="34" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I5" s="34" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J5" s="34" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5263,7 +5347,7 @@
       <c r="D6" s="36"/>
       <c r="E6" s="36"/>
       <c r="F6" s="36" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G6" s="58" t="n">
         <f aca="false">Instruments!F6</f>
@@ -5291,7 +5375,7 @@
       <c r="D7" s="36"/>
       <c r="E7" s="36"/>
       <c r="F7" s="36" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G7" s="58" t="n">
         <f aca="false">Instruments!F7</f>
@@ -5319,7 +5403,7 @@
       <c r="D8" s="36"/>
       <c r="E8" s="36"/>
       <c r="F8" s="36" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G8" s="58" t="n">
         <f aca="false">Instruments!F8</f>
@@ -5347,7 +5431,7 @@
       <c r="D9" s="36"/>
       <c r="E9" s="36"/>
       <c r="F9" s="36" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G9" s="58" t="n">
         <f aca="false">Instruments!F9</f>
@@ -5375,7 +5459,7 @@
       <c r="D10" s="36"/>
       <c r="E10" s="36"/>
       <c r="F10" s="36" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G10" s="58" t="n">
         <f aca="false">Instruments!F10</f>
@@ -5403,7 +5487,7 @@
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
       <c r="F11" s="36" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G11" s="58" t="n">
         <f aca="false">Instruments!F11</f>
@@ -5431,7 +5515,7 @@
       <c r="D12" s="36"/>
       <c r="E12" s="36"/>
       <c r="F12" s="36" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G12" s="58" t="n">
         <f aca="false">Instruments!F12</f>
@@ -5459,7 +5543,7 @@
       <c r="D13" s="36"/>
       <c r="E13" s="36"/>
       <c r="F13" s="36" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G13" s="58" t="n">
         <f aca="false">Instruments!F13</f>
@@ -5487,7 +5571,7 @@
       <c r="D14" s="36"/>
       <c r="E14" s="36"/>
       <c r="F14" s="36" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G14" s="58" t="n">
         <f aca="false">Instruments!F14</f>
@@ -5515,7 +5599,7 @@
       <c r="D15" s="36"/>
       <c r="E15" s="36"/>
       <c r="F15" s="36" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G15" s="58" t="n">
         <f aca="false">Instruments!F15</f>
@@ -5537,17 +5621,17 @@
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="57" t="str">
         <f aca="false">Instruments!B16</f>
-        <v>Copper</v>
+        <v>Brent Crude</v>
       </c>
       <c r="C16" s="38"/>
       <c r="D16" s="36"/>
       <c r="E16" s="36"/>
       <c r="F16" s="36" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G16" s="58" t="n">
         <f aca="false">Instruments!F16</f>
-        <v>10000</v>
+        <v>69</v>
       </c>
       <c r="H16" s="59" t="str">
         <f aca="false">IF(ISNUMBER(C16),C16/G16-1,"n/a")</f>
@@ -5565,17 +5649,17 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="57" t="str">
         <f aca="false">Instruments!B17</f>
-        <v>Natural Gas</v>
+        <v>Copper</v>
       </c>
       <c r="C17" s="38"/>
       <c r="D17" s="36"/>
       <c r="E17" s="36"/>
       <c r="F17" s="36" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G17" s="58" t="n">
         <f aca="false">Instruments!F17</f>
-        <v>3.5</v>
+        <v>10000</v>
       </c>
       <c r="H17" s="59" t="str">
         <f aca="false">IF(ISNUMBER(C17),C17/G17-1,"n/a")</f>
@@ -5593,17 +5677,17 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="57" t="str">
         <f aca="false">Instruments!B18</f>
-        <v>Custom (edit me)</v>
+        <v>Natural Gas</v>
       </c>
       <c r="C18" s="38"/>
       <c r="D18" s="36"/>
       <c r="E18" s="36"/>
       <c r="F18" s="36" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G18" s="58" t="n">
         <f aca="false">Instruments!F18</f>
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="H18" s="59" t="str">
         <f aca="false">IF(ISNUMBER(C18),C18/G18-1,"n/a")</f>
@@ -5618,8 +5702,36 @@
         <v>n/a</v>
       </c>
     </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="57" t="str">
+        <f aca="false">Instruments!B19</f>
+        <v>Custom (edit me)</v>
+      </c>
+      <c r="C19" s="38"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36" t="s">
+        <v>198</v>
+      </c>
+      <c r="G19" s="58" t="n">
+        <f aca="false">Instruments!F19</f>
+        <v>4.2</v>
+      </c>
+      <c r="H19" s="59" t="str">
+        <f aca="false">IF(ISNUMBER(C19),C19/G19-1,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="I19" s="60" t="str">
+        <f aca="false">IF(ISNUMBER(C19),C19*(1+Instruments!J19*Instruments!M19/Instruments!L19)/(1+Instruments!G19*Instruments!M19/Instruments!K19),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="J19" s="61" t="str">
+        <f aca="false">IF(ISNUMBER(C19),(I19-C19)/Instruments!N19,"n/a")</f>
+        <v>n/a</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B6:J18">
+  <conditionalFormatting sqref="B6:J19">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$B6=Instrument</formula>
     </cfRule>
@@ -5658,12 +5770,12 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -5700,7 +5812,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="8" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C8" s="17" t="n">
         <f aca="false">C5*C7/C6</f>
@@ -5713,7 +5825,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C9" s="64" t="n">
         <f aca="false">(C8-C5)/Tick</f>
@@ -5722,7 +5834,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C10" s="65" t="n">
         <f aca="false">(C8/C5-1)*365/Tenor_Days</f>
@@ -5731,7 +5843,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C11" s="65" t="n">
         <f aca="false">Rate_B-Rate_A</f>
@@ -5740,14 +5852,14 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C14" s="66" t="n">
         <v>2</v>
@@ -5765,7 +5877,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C16" s="67" t="n">
         <f aca="false">C15/Pos_Limit</f>
@@ -5774,7 +5886,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="8" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C17" s="68" t="n">
         <f aca="false">-MAX(-1,MIN(1,C16))*Max_Skew_Ticks</f>
@@ -5783,7 +5895,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">ROUND(C8/Tick+C17-Spread_Ticks/2,0)*Tick</f>
@@ -5792,7 +5904,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="8" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C19" s="17" t="n">
         <f aca="false">C18+Spread_Ticks*Tick</f>
@@ -5801,7 +5913,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C20" s="68" t="n">
         <f aca="false">(C19-C18)/Tick</f>
@@ -5810,7 +5922,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C21" s="68" t="n">
         <f aca="false">((C18+C19)/2-C8)/Tick</f>
@@ -5829,7 +5941,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C23" s="27" t="n">
         <f aca="false">C15-Clip_Size</f>
@@ -5838,7 +5950,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="8" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C24" s="27" t="n">
         <f aca="false">C15+Clip_Size</f>
@@ -5847,7 +5959,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C25" s="12" t="str">
         <f aca="false">IF(OR(ABS(C23)&gt;Pos_Limit,ABS(C24)&gt;Pos_Limit),"YES: a fill can breach the limit","No")</f>
@@ -5856,7 +5968,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -5866,22 +5978,22 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="69" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C29" s="69" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D29" s="69" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E29" s="69" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F29" s="69" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G29" s="69" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6282,55 +6394,55 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="75" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B4" s="75"/>
       <c r="C4" s="75"/>
       <c r="D4" s="75" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E4" s="75"/>
       <c r="F4" s="75"/>
       <c r="G4" s="75" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H4" s="75"/>
       <c r="I4" s="75"/>
       <c r="J4" s="75" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K4" s="75"/>
       <c r="L4" s="75"/>
       <c r="M4" s="75" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="N4" s="75"/>
       <c r="O4" s="75"/>
       <c r="P4" s="75"/>
       <c r="Q4" s="75" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="R4" s="75"/>
       <c r="S4" s="75"/>
       <c r="T4" s="75"/>
       <c r="U4" s="75" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="V4" s="75"/>
       <c r="W4" s="75"/>
       <c r="X4" s="75"/>
       <c r="Y4" s="75" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Z4" s="75"/>
       <c r="AA4" s="75"/>
@@ -6339,13 +6451,13 @@
     </row>
     <row r="5" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="34" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D5" s="34" t="s">
         <v>125</v>
@@ -6361,29 +6473,29 @@
         <v>Opening position (USD)</v>
       </c>
       <c r="H5" s="34" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I5" s="34" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J5" s="34" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="K5" s="34" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L5" s="34" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M5" s="34" t="str">
         <f aca="false">"Client fill ("&amp;Unit_Label&amp;", + = we buy)"</f>
         <v>Client fill (USD, + = we buy)</v>
       </c>
       <c r="N5" s="34" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O5" s="34" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P5" s="34" t="str">
         <f aca="false">"Spread capture ("&amp;PnL_Ccy&amp;")"</f>
@@ -6398,20 +6510,20 @@
         <v>Cum. P&amp;L before hedge (SGD)</v>
       </c>
       <c r="S5" s="34" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="T5" s="34" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="U5" s="34" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="V5" s="34" t="str">
         <f aca="false">"Hedge qty ("&amp;Unit_Label&amp;", + = we buy)"</f>
         <v>Hedge qty (USD, + = we buy)</v>
       </c>
       <c r="W5" s="34" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="X5" s="34" t="str">
         <f aca="false">"Hedge cost ("&amp;PnL_Ccy&amp;")"</f>
@@ -6430,7 +6542,7 @@
         <v>Cumulative P&amp;L (SGD)</v>
       </c>
       <c r="AB5" s="34" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AC5" s="34" t="str">
         <f aca="false">"Closing position value ("&amp;PnL_Ccy&amp;")"</f>
@@ -6502,7 +6614,7 @@
         <v>1.8</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D7" s="45" t="n">
         <f aca="false">D6+B7*Step_Vol_Ticks*Tick</f>
@@ -6618,7 +6730,7 @@
         <v>-1.3</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D8" s="45" t="n">
         <f aca="false">D7+B8*Step_Vol_Ticks*Tick</f>
@@ -6734,7 +6846,7 @@
         <v>-0.4</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D9" s="45" t="n">
         <f aca="false">D8+B9*Step_Vol_Ticks*Tick</f>
@@ -6850,7 +6962,7 @@
         <v>1.2</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D10" s="45" t="n">
         <f aca="false">D9+B10*Step_Vol_Ticks*Tick</f>
@@ -6966,7 +7078,7 @@
         <v>0.2</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D11" s="45" t="n">
         <f aca="false">D10+B11*Step_Vol_Ticks*Tick</f>
@@ -7082,7 +7194,7 @@
         <v>-0.3</v>
       </c>
       <c r="C12" s="50" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D12" s="45" t="n">
         <f aca="false">D11+B12*Step_Vol_Ticks*Tick</f>
@@ -7198,7 +7310,7 @@
         <v>-0.7</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D13" s="45" t="n">
         <f aca="false">D12+B13*Step_Vol_Ticks*Tick</f>
@@ -7314,7 +7426,7 @@
         <v>0</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D14" s="45" t="n">
         <f aca="false">D13+B14*Step_Vol_Ticks*Tick</f>
@@ -7430,7 +7542,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D15" s="45" t="n">
         <f aca="false">D14+B15*Step_Vol_Ticks*Tick</f>
@@ -7546,7 +7658,7 @@
         <v>0.4</v>
       </c>
       <c r="C16" s="50" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D16" s="45" t="n">
         <f aca="false">D15+B16*Step_Vol_Ticks*Tick</f>
@@ -7662,7 +7774,7 @@
         <v>0.2</v>
       </c>
       <c r="C17" s="50" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D17" s="45" t="n">
         <f aca="false">D16+B17*Step_Vol_Ticks*Tick</f>
@@ -7778,7 +7890,7 @@
         <v>0.3</v>
       </c>
       <c r="C18" s="50" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D18" s="45" t="n">
         <f aca="false">D17+B18*Step_Vol_Ticks*Tick</f>
@@ -7894,7 +8006,7 @@
         <v>0.2</v>
       </c>
       <c r="C19" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D19" s="45" t="n">
         <f aca="false">D18+B19*Step_Vol_Ticks*Tick</f>
@@ -8010,7 +8122,7 @@
         <v>-1.1</v>
       </c>
       <c r="C20" s="50" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D20" s="45" t="n">
         <f aca="false">D19+B20*Step_Vol_Ticks*Tick</f>
@@ -8126,7 +8238,7 @@
         <v>-2.6</v>
       </c>
       <c r="C21" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D21" s="45" t="n">
         <f aca="false">D20+B21*Step_Vol_Ticks*Tick</f>
@@ -8242,7 +8354,7 @@
         <v>-1</v>
       </c>
       <c r="C22" s="50" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D22" s="45" t="n">
         <f aca="false">D21+B22*Step_Vol_Ticks*Tick</f>
@@ -8358,7 +8470,7 @@
         <v>-1</v>
       </c>
       <c r="C23" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D23" s="45" t="n">
         <f aca="false">D22+B23*Step_Vol_Ticks*Tick</f>
@@ -8474,7 +8586,7 @@
         <v>1.2</v>
       </c>
       <c r="C24" s="50" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D24" s="45" t="n">
         <f aca="false">D23+B24*Step_Vol_Ticks*Tick</f>
@@ -8590,7 +8702,7 @@
         <v>-1.8</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D25" s="45" t="n">
         <f aca="false">D24+B25*Step_Vol_Ticks*Tick</f>
@@ -8706,7 +8818,7 @@
         <v>0.5</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D26" s="45" t="n">
         <f aca="false">D25+B26*Step_Vol_Ticks*Tick</f>
@@ -8822,7 +8934,7 @@
         <v>0</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D27" s="45" t="n">
         <f aca="false">D26+B27*Step_Vol_Ticks*Tick</f>
@@ -8938,7 +9050,7 @@
         <v>0.2</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D28" s="45" t="n">
         <f aca="false">D27+B28*Step_Vol_Ticks*Tick</f>
@@ -9054,7 +9166,7 @@
         <v>-0.1</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D29" s="45" t="n">
         <f aca="false">D28+B29*Step_Vol_Ticks*Tick</f>
@@ -9170,7 +9282,7 @@
         <v>-1.3</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D30" s="45" t="n">
         <f aca="false">D29+B30*Step_Vol_Ticks*Tick</f>
@@ -9286,7 +9398,7 @@
         <v>0.4</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D31" s="45" t="n">
         <f aca="false">D30+B31*Step_Vol_Ticks*Tick</f>
@@ -9402,7 +9514,7 @@
         <v>0.7</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D32" s="45" t="n">
         <f aca="false">D31+B32*Step_Vol_Ticks*Tick</f>
@@ -9518,7 +9630,7 @@
         <v>-1.3</v>
       </c>
       <c r="C33" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D33" s="45" t="n">
         <f aca="false">D32+B33*Step_Vol_Ticks*Tick</f>
@@ -9634,7 +9746,7 @@
         <v>-1.5</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D34" s="45" t="n">
         <f aca="false">D33+B34*Step_Vol_Ticks*Tick</f>
@@ -9750,7 +9862,7 @@
         <v>-1.9</v>
       </c>
       <c r="C35" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D35" s="45" t="n">
         <f aca="false">D34+B35*Step_Vol_Ticks*Tick</f>
@@ -9866,7 +9978,7 @@
         <v>-1.5</v>
       </c>
       <c r="C36" s="50" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D36" s="45" t="n">
         <f aca="false">D35+B36*Step_Vol_Ticks*Tick</f>
@@ -9982,7 +10094,7 @@
         <v>-0.8</v>
       </c>
       <c r="C37" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D37" s="45" t="n">
         <f aca="false">D36+B37*Step_Vol_Ticks*Tick</f>
@@ -10098,7 +10210,7 @@
         <v>-0.5</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D38" s="45" t="n">
         <f aca="false">D37+B38*Step_Vol_Ticks*Tick</f>
@@ -10214,7 +10326,7 @@
         <v>-1.5</v>
       </c>
       <c r="C39" s="50" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D39" s="45" t="n">
         <f aca="false">D38+B39*Step_Vol_Ticks*Tick</f>
@@ -10330,7 +10442,7 @@
         <v>-0.3</v>
       </c>
       <c r="C40" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D40" s="45" t="n">
         <f aca="false">D39+B40*Step_Vol_Ticks*Tick</f>
@@ -10446,7 +10558,7 @@
         <v>-0.4</v>
       </c>
       <c r="C41" s="50" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D41" s="45" t="n">
         <f aca="false">D40+B41*Step_Vol_Ticks*Tick</f>
@@ -10562,7 +10674,7 @@
         <v>-0.9</v>
       </c>
       <c r="C42" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D42" s="45" t="n">
         <f aca="false">D41+B42*Step_Vol_Ticks*Tick</f>
@@ -10678,7 +10790,7 @@
         <v>-1.5</v>
       </c>
       <c r="C43" s="50" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D43" s="45" t="n">
         <f aca="false">D42+B43*Step_Vol_Ticks*Tick</f>
@@ -10794,7 +10906,7 @@
         <v>-1.4</v>
       </c>
       <c r="C44" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D44" s="45" t="n">
         <f aca="false">D43+B44*Step_Vol_Ticks*Tick</f>
@@ -10910,7 +11022,7 @@
         <v>-0.9</v>
       </c>
       <c r="C45" s="50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D45" s="45" t="n">
         <f aca="false">D44+B45*Step_Vol_Ticks*Tick</f>
@@ -11026,7 +11138,7 @@
         <v>-2.5</v>
       </c>
       <c r="C46" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D46" s="45" t="n">
         <f aca="false">D45+B46*Step_Vol_Ticks*Tick</f>
@@ -11142,7 +11254,7 @@
         <v>-1.1</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D47" s="45" t="n">
         <f aca="false">D46+B47*Step_Vol_Ticks*Tick</f>
@@ -11258,7 +11370,7 @@
         <v>-0.4</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D48" s="45" t="n">
         <f aca="false">D47+B48*Step_Vol_Ticks*Tick</f>
@@ -11374,7 +11486,7 @@
         <v>0.1</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D49" s="45" t="n">
         <f aca="false">D48+B49*Step_Vol_Ticks*Tick</f>
@@ -11490,7 +11602,7 @@
         <v>0.3</v>
       </c>
       <c r="C50" s="50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D50" s="45" t="n">
         <f aca="false">D49+B50*Step_Vol_Ticks*Tick</f>
@@ -11606,7 +11718,7 @@
         <v>0.5</v>
       </c>
       <c r="C51" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D51" s="45" t="n">
         <f aca="false">D50+B51*Step_Vol_Ticks*Tick</f>
@@ -11722,7 +11834,7 @@
         <v>-0.2</v>
       </c>
       <c r="C52" s="50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D52" s="45" t="n">
         <f aca="false">D51+B52*Step_Vol_Ticks*Tick</f>
@@ -11838,7 +11950,7 @@
         <v>-0.9</v>
       </c>
       <c r="C53" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D53" s="45" t="n">
         <f aca="false">D52+B53*Step_Vol_Ticks*Tick</f>
@@ -11954,7 +12066,7 @@
         <v>0.5</v>
       </c>
       <c r="C54" s="50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D54" s="45" t="n">
         <f aca="false">D53+B54*Step_Vol_Ticks*Tick</f>
@@ -12070,7 +12182,7 @@
         <v>0.5</v>
       </c>
       <c r="C55" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D55" s="45" t="n">
         <f aca="false">D54+B55*Step_Vol_Ticks*Tick</f>
@@ -12186,7 +12298,7 @@
         <v>-1.7</v>
       </c>
       <c r="C56" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D56" s="45" t="n">
         <f aca="false">D55+B56*Step_Vol_Ticks*Tick</f>
@@ -12302,7 +12414,7 @@
         <v>-0.7</v>
       </c>
       <c r="C57" s="50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D57" s="45" t="n">
         <f aca="false">D56+B57*Step_Vol_Ticks*Tick</f>
@@ -12418,7 +12530,7 @@
         <v>-1.5</v>
       </c>
       <c r="C58" s="50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D58" s="45" t="n">
         <f aca="false">D57+B58*Step_Vol_Ticks*Tick</f>
@@ -12534,7 +12646,7 @@
         <v>-0.2</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D59" s="45" t="n">
         <f aca="false">D58+B59*Step_Vol_Ticks*Tick</f>
@@ -12650,7 +12762,7 @@
         <v>0.4</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D60" s="45" t="n">
         <f aca="false">D59+B60*Step_Vol_Ticks*Tick</f>
@@ -12766,7 +12878,7 @@
         <v>-0.5</v>
       </c>
       <c r="C61" s="50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D61" s="45" t="n">
         <f aca="false">D60+B61*Step_Vol_Ticks*Tick</f>
@@ -12882,7 +12994,7 @@
         <v>0</v>
       </c>
       <c r="C62" s="50" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D62" s="45" t="n">
         <f aca="false">D61+B62*Step_Vol_Ticks*Tick</f>
@@ -12998,7 +13110,7 @@
         <v>0.2</v>
       </c>
       <c r="C63" s="50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D63" s="45" t="n">
         <f aca="false">D62+B63*Step_Vol_Ticks*Tick</f>
@@ -13114,7 +13226,7 @@
         <v>0.2</v>
       </c>
       <c r="C64" s="50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D64" s="45" t="n">
         <f aca="false">D63+B64*Step_Vol_Ticks*Tick</f>
@@ -13230,7 +13342,7 @@
         <v>0.4</v>
       </c>
       <c r="C65" s="50" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D65" s="45" t="n">
         <f aca="false">D64+B65*Step_Vol_Ticks*Tick</f>
@@ -13346,7 +13458,7 @@
         <v>-0.5</v>
       </c>
       <c r="C66" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D66" s="45" t="n">
         <f aca="false">D65+B66*Step_Vol_Ticks*Tick</f>
@@ -13517,19 +13629,19 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C5" s="22" t="n">
         <f aca="false">COUNT(Simulation!$A$7:$A$66)</f>
@@ -13539,19 +13651,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="8" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C6" s="22" t="n">
         <f aca="false">COUNTIF(Simulation!$M$7:$M$66,"&lt;&gt;0")</f>
         <v>26</v>
       </c>
       <c r="D6" s="92" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C7" s="22" t="n">
         <f aca="false">COUNTIF(Simulation!$M$7:$M$66,"&lt;0")</f>
@@ -13561,7 +13673,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C8" s="22" t="n">
         <f aca="false">COUNTIF(Simulation!$M$7:$M$66,"&gt;0")</f>
@@ -13582,19 +13694,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C10" s="22" t="n">
         <f aca="false">SUMPRODUCT((Simulation!$S$7:$S$66=1)*(Simulation!$T$7:$T$66=0))</f>
         <v>2</v>
       </c>
       <c r="D10" s="92" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="8" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C11" s="22" t="n">
         <f aca="false">SUM(Simulation!$T$7:$T$66)</f>
@@ -13615,7 +13727,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -13630,7 +13742,7 @@
         <v>1250000</v>
       </c>
       <c r="D15" s="92" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13643,7 +13755,7 @@
         <v>1000000</v>
       </c>
       <c r="D16" s="92" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13670,19 +13782,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="8" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C19" s="67" t="n">
         <f aca="false">MAX(0,-C18)/Loss_Limit</f>
         <v>1.07118172455797</v>
       </c>
       <c r="D19" s="92" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="8" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C20" s="12" t="str">
         <f aca="false">IF(Simulation!$AB$66=1,"YES","NO")</f>
@@ -13692,7 +13804,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="8" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C21" s="22" t="n">
         <f aca="false">IFERROR(INDEX(Simulation!$A$7:$A$66,MATCH(1,Simulation!$T$7:$T$66,0)),"n/a")</f>
@@ -13710,7 +13822,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="8" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C24" s="93" t="n">
         <f aca="false">SUM(Simulation!$P$7:$P$66)</f>
@@ -13720,19 +13832,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="8" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C25" s="93" t="n">
         <f aca="false">SUM(Simulation!$Q$7:$Q$66)</f>
         <v>-3651.72822531124</v>
       </c>
       <c r="D25" s="92" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="8" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C26" s="93" t="n">
         <f aca="false">SUM(Simulation!$X$7:$X$66)</f>
@@ -13742,7 +13854,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C27" s="94" t="n">
         <f aca="false">SUM(C24:C26)</f>
@@ -13752,7 +13864,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="8" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C28" s="93" t="n">
         <f aca="false">Simulation!$AA$66</f>
@@ -13762,45 +13874,45 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C31" s="12" t="str">
         <f aca="false">IF(ABS(C27-C28)&lt;0.005,"OK","ERROR")</f>
         <v>OK</v>
       </c>
       <c r="D31" s="92" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C32" s="12" t="str">
         <f aca="false">IF(ABS(Start_Pos+SUM(Simulation!$M$7:$M$66)+SUM(Simulation!$V$7:$V$66)-Simulation!$Y$66)&lt;0.5,"OK","ERROR")</f>
         <v>OK</v>
       </c>
       <c r="D32" s="92" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C33" s="12" t="str">
         <f aca="false">IF(SUMPRODUCT((Simulation!$Y$7:$Y$66&lt;&gt;0)*(ABS(Simulation!$Y$7:$Y$66)&gt;Pos_Limit))=0,"OK","ERROR")</f>
         <v>OK</v>
       </c>
       <c r="D33" s="92" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>

--- a/excel/Forwards_Market_Making_Simulator.xlsx
+++ b/excel/Forwards_Market_Making_Simulator.xlsx
@@ -2097,11 +2097,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="24287577"/>
-        <c:axId val="28259607"/>
+        <c:axId val="36838534"/>
+        <c:axId val="23622421"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="24287577"/>
+        <c:axId val="36838534"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2167,7 +2167,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28259607"/>
+        <c:crossAx val="23622421"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2175,7 +2175,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="28259607"/>
+        <c:axId val="23622421"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2251,7 +2251,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24287577"/>
+        <c:crossAx val="36838534"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2769,11 +2769,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="90674721"/>
-        <c:axId val="37613774"/>
+        <c:axId val="60224229"/>
+        <c:axId val="70253935"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="90674721"/>
+        <c:axId val="60224229"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2839,7 +2839,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37613774"/>
+        <c:crossAx val="70253935"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2847,7 +2847,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37613774"/>
+        <c:axId val="70253935"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2923,7 +2923,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90674721"/>
+        <c:crossAx val="60224229"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
